--- a/output/lgbm_reg/04_model_report/LightGBM_回归评估_自定义分桶.xlsx
+++ b/output/lgbm_reg/04_model_report/LightGBM_回归评估_自定义分桶.xlsx
@@ -490,31 +490,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.732</v>
+        <v>0.5037</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4891</v>
+        <v>0.3937</v>
       </c>
       <c r="D2" t="n">
-        <v>0.872</v>
+        <v>0.9394</v>
       </c>
       <c r="E2" t="n">
-        <v>266.2461</v>
+        <v>105.6396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9436</v>
+        <v>0.9694</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9691</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>195</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="3">
@@ -524,31 +524,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8734</v>
+        <v>0.5385</v>
       </c>
       <c r="C3" t="n">
-        <v>0.657</v>
+        <v>0.4197</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8109</v>
+        <v>0.9331</v>
       </c>
       <c r="E3" t="n">
-        <v>85.1658</v>
+        <v>103.5968</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9084</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9392</v>
+        <v>0.9648</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>49</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4">
@@ -558,31 +558,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7659</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5506</v>
+        <v>0.4213</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8608</v>
+        <v>0.9258</v>
       </c>
       <c r="E4" t="n">
-        <v>108.2847</v>
+        <v>90.28530000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9354</v>
+        <v>0.9627</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9573</v>
+        <v>0.9603</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2756</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -596,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,17 +657,17 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>误差(预测-真实)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MAPE(%)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>误差(预测-真实)</t>
         </is>
       </c>
     </row>
@@ -682,41 +682,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[-7.2526, -2.96955]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>211</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1026</v>
+        <v>0.1032</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.2526</v>
+        <v>-8.161</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.0051</v>
+        <v>-3.0009</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.1625</v>
+        <v>-4.0079</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.2796</v>
+        <v>-3.7731</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.5446</v>
+        <v>-5.4386</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.8474</v>
+        <v>-2.0001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9608</v>
+        <v>0.2348</v>
       </c>
       <c r="M2" t="n">
-        <v>18.9506</v>
+        <v>0.4766</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8829</v>
+        <v>11.7466</v>
       </c>
     </row>
     <row r="3">
@@ -730,41 +730,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(-2.96955, -0.99345]</t>
+          <t>(-3, -1]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>581</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2615</v>
+        <v>0.2841</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.934</v>
+        <v>-2.9992</v>
       </c>
       <c r="G3" t="n">
         <v>-1.0048</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.7611</v>
+        <v>-1.8659</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.675</v>
+        <v>-1.7897</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.2659</v>
+        <v>-3.6812</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2352</v>
+        <v>0.2086</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3263</v>
+        <v>0.0762</v>
       </c>
       <c r="M3" t="n">
-        <v>20.0186</v>
+        <v>0.3641</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0861</v>
+        <v>21.5606</v>
       </c>
     </row>
     <row r="4">
@@ -778,41 +778,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(-0.99345, -0.03385]</t>
+          <t>(-1, 0]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>382</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.1868</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9821</v>
+        <v>-0.9996</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0694</v>
+        <v>-0.0017</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5563</v>
+        <v>-0.5087</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4084</v>
+        <v>-0.4758</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.635</v>
+        <v>-1.9753</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6878</v>
+        <v>0.975</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4037</v>
+        <v>0.0329</v>
       </c>
       <c r="M4" t="n">
-        <v>121.1112</v>
+        <v>0.3707</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1479</v>
+        <v>230.8947</v>
       </c>
     </row>
     <row r="5">
@@ -826,41 +826,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(-0.03385, 0.9971]</t>
+          <t>(0, 1]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>38</v>
+        <v>381</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1949</v>
+        <v>0.1863</v>
       </c>
       <c r="F5" t="n">
         <v>0.0017</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9926</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4922</v>
+        <v>0.4945</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3449</v>
+        <v>0.4281</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6037</v>
+        <v>-1.1029</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3635</v>
+        <v>1.9153</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3641</v>
+        <v>-0.0664</v>
       </c>
       <c r="M5" t="n">
-        <v>1170.6666</v>
+        <v>0.3731</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1473</v>
+        <v>268.5155</v>
       </c>
     </row>
     <row r="6">
@@ -874,41 +874,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(0.9971, 3.0766]</t>
+          <t>(1, 3]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>39</v>
+        <v>403</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>0.1971</v>
       </c>
       <c r="F6" t="n">
         <v>1.0016</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9963</v>
+        <v>2.9966</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8157</v>
+        <v>1.8564</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5527</v>
+        <v>1.7581</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1416</v>
+        <v>0.0162</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1895</v>
+        <v>4.0538</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4141</v>
+        <v>-0.0983</v>
       </c>
       <c r="M6" t="n">
-        <v>24.7334</v>
+        <v>0.3919</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.263</v>
+        <v>23.0386</v>
       </c>
     </row>
     <row r="7">
@@ -922,89 +922,91 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(3.0766, 5.0809]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="E7" t="n">
-        <v>0.041</v>
+        <v>0.0425</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1569</v>
+        <v>3.0899</v>
       </c>
       <c r="G7" t="n">
-        <v>5.0809</v>
+        <v>7.4881</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8758</v>
+        <v>3.8867</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1519</v>
+        <v>3.4088</v>
       </c>
       <c r="J7" t="n">
-        <v>1.98</v>
+        <v>1.2835</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2125</v>
+        <v>4.2053</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7239</v>
+        <v>-0.4779</v>
       </c>
       <c r="M7" t="n">
-        <v>43.0948</v>
+        <v>0.5904</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7239</v>
+        <v>14.2193</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>验证集</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+          <t>训练集</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2045</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[-4.0899, -3.36605]</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.0408</v>
-      </c>
       <c r="F8" t="n">
-        <v>-4.0899</v>
+        <v>-8.161</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8501</v>
+        <v>7.4881</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.97</v>
+        <v>-0.4154</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.0557</v>
+        <v>-0.4154</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.1635</v>
+        <v>-5.4386</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.9478</v>
+        <v>4.2053</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9143</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>22.8791</v>
+        <v>0.3937</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9143</v>
+        <v>105.6396</v>
       </c>
     </row>
     <row r="9">
@@ -1014,45 +1016,45 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(-3.36605, -0.98025]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3061</v>
+        <v>0.1191</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.882</v>
+        <v>-7.2526</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0079</v>
+        <v>-3.0081</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7281</v>
+        <v>-3.9637</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7687</v>
+        <v>-3.658</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.2373</v>
+        <v>-5.4514</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.105</v>
+        <v>-2.2235</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6264</v>
+        <v>0.3057</v>
       </c>
       <c r="M9" t="n">
-        <v>38.7223</v>
+        <v>0.5404</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0406</v>
+        <v>13.6211</v>
       </c>
     </row>
     <row r="10">
@@ -1062,45 +1064,45 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(-0.98025, -0.09535]</t>
+          <t>(-3, -1]</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>158</v>
       </c>
       <c r="E10" t="n">
-        <v>0.102</v>
+        <v>0.3086</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9526</v>
+        <v>-2.9737</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2445</v>
+        <v>-1.0059</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5648</v>
+        <v>-1.8736</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.724</v>
+        <v>-1.7968</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2291</v>
+        <v>-3.4527</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2952</v>
+        <v>0.037</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4234</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>82.27249999999999</v>
+        <v>0.3813</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1592</v>
+        <v>22.5625</v>
       </c>
     </row>
     <row r="11">
@@ -1110,45 +1112,45 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(-0.09535, 0.9764]</t>
+          <t>(-1, 0]</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2245</v>
+        <v>0.1816</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0538</v>
+        <v>-0.9991</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9204</v>
+        <v>-0.0058</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4873</v>
+        <v>-0.5215</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3327</v>
+        <v>-0.4716</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.571</v>
+        <v>-2.0491</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8474</v>
+        <v>1.108</v>
       </c>
       <c r="L11" t="n">
-        <v>0.468</v>
+        <v>0.0499</v>
       </c>
       <c r="M11" t="n">
-        <v>237.2746</v>
+        <v>0.4518</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1546</v>
+        <v>184.7318</v>
       </c>
     </row>
     <row r="12">
@@ -1158,45 +1160,45 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(0.9764, 2.99805]</t>
+          <t>(0, 1]</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2245</v>
+        <v>0.1797</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0324</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7019</v>
+        <v>0.9588</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6517</v>
+        <v>0.4406</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6778</v>
+        <v>0.3904</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8137</v>
+        <v>-0.8394</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1604</v>
+        <v>1.6601</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4231</v>
+        <v>-0.0502</v>
       </c>
       <c r="M12" t="n">
-        <v>27.6623</v>
+        <v>0.3603</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0261</v>
+        <v>317.4007</v>
       </c>
     </row>
     <row r="13">
@@ -1206,141 +1208,143 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(2.99805, 5.303]</t>
+          <t>(1, 3]</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="E13" t="n">
-        <v>0.102</v>
+        <v>0.1523</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2942</v>
+        <v>1.0092</v>
       </c>
       <c r="G13" t="n">
-        <v>5.303</v>
+        <v>2.9371</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9682</v>
+        <v>1.8035</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1581</v>
+        <v>1.6911</v>
       </c>
       <c r="J13" t="n">
-        <v>2.108</v>
+        <v>-0.1955</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1773</v>
+        <v>3.8916</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8102</v>
+        <v>-0.1124</v>
       </c>
       <c r="M13" t="n">
-        <v>44.1729</v>
+        <v>0.4151</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8101</v>
+        <v>24.4883</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OOT</t>
+          <t>验证集</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[-8.161, -3.00005]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>287</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1041</v>
+        <v>0.0586</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.161</v>
+        <v>3.0061</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.0009</v>
+        <v>6.3529</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.9677</v>
+        <v>3.7386</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.1136</v>
+        <v>3.402</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.5586</v>
+        <v>1.8332</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.4998</v>
+        <v>4.1762</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8858</v>
+        <v>-0.3366</v>
       </c>
       <c r="M14" t="n">
-        <v>20.2351</v>
+        <v>0.4708</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8541</v>
+        <v>11.8263</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OOT</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
+          <t>验证集</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(-3.00005, -1.0008]</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>800</v>
+        <v>512</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2903</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.9992</v>
+        <v>-7.2526</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.002</v>
+        <v>6.3529</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.8802</v>
+        <v>-0.5722</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7254</v>
+        <v>-0.5488</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.5042</v>
+        <v>-5.4514</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6946</v>
+        <v>4.1762</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4643</v>
+        <v>0.0234</v>
       </c>
       <c r="M15" t="n">
-        <v>27.5607</v>
+        <v>0.4197</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1548</v>
+        <v>103.5968</v>
       </c>
     </row>
     <row r="16">
@@ -1350,45 +1354,45 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(-1.0008, 0.0031]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>517</v>
+        <v>37</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1876</v>
+        <v>0.0835</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9996</v>
+        <v>-6.5133</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0017</v>
+        <v>-3.0053</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5027</v>
+        <v>-3.8505</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3514</v>
+        <v>-3.5694</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.3012</v>
+        <v>-5.2661</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2115</v>
+        <v>-1.979</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4351</v>
+        <v>0.2811</v>
       </c>
       <c r="M16" t="n">
-        <v>249.3575</v>
+        <v>0.4328</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1513</v>
+        <v>11.6289</v>
       </c>
     </row>
     <row r="17">
@@ -1398,45 +1402,45 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(0.0031, 1.00115]</t>
+          <t>(-3, -1]</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>503</v>
+        <v>127</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1825</v>
+        <v>0.2867</v>
       </c>
       <c r="F17" t="n">
-        <v>0.007900000000000001</v>
+        <v>-2.9675</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9995000000000001</v>
+        <v>-1.002</v>
       </c>
       <c r="H17" t="n">
-        <v>0.479</v>
+        <v>-1.8883</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4898</v>
+        <v>-1.7633</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1951</v>
+        <v>-3.9434</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0649</v>
+        <v>0.109</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3893</v>
+        <v>0.125</v>
       </c>
       <c r="M17" t="n">
-        <v>242.6426</v>
+        <v>0.3973</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0108</v>
+        <v>22.8551</v>
       </c>
     </row>
     <row r="18">
@@ -1446,45 +1450,45 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(1.00115, 3.00135]</t>
+          <t>(-1, 0]</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>519</v>
+        <v>86</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1883</v>
+        <v>0.1941</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0028</v>
+        <v>-0.9921</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9966</v>
+        <v>-0.0215</v>
       </c>
       <c r="H18" t="n">
-        <v>1.837</v>
+        <v>-0.4834</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5589</v>
+        <v>-0.3848</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3679</v>
+        <v>-1.8881</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2034</v>
+        <v>1.1113</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4585</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>26.7526</v>
+        <v>0.4084</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2781</v>
+        <v>177.945</v>
       </c>
     </row>
     <row r="19">
@@ -1494,48 +1498,204 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>(0, 1]</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>79</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9853</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1.2688</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.7226</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.081</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="N19" t="n">
+        <v>235.1902</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>(1, 3]</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>88</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1986</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.0109</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.996</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.7454</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.5569</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.0094</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.5715</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.1885</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="N20" t="n">
+        <v>27.5321</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>6</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>(3.00135, 7.636]</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>130</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.0472</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3.0061</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>(3, +inf]</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>26</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0587</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.0415</v>
+      </c>
+      <c r="G21" t="n">
         <v>7.636</v>
       </c>
-      <c r="H19" t="n">
-        <v>3.8964</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.104</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.7612</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.211</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.7925</v>
-      </c>
-      <c r="M19" t="n">
-        <v>44.0391</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-1.7924</v>
+      <c r="H21" t="n">
+        <v>4.1186</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.5159</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.5441</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1374</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.6027</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.6395</v>
+      </c>
+      <c r="N21" t="n">
+        <v>13.7458</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>443</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-6.5133</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7.636</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.2869</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.2958</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-5.2661</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.1374</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="N22" t="n">
+        <v>90.28530000000001</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="N2:N22">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1546,7 +1706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1607,17 +1767,17 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>误差(预测-真实)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MAPE(%)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>误差(预测-真实)</t>
         </is>
       </c>
     </row>
@@ -1632,41 +1792,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[-3.5446, -3.0]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>202</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0988</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.2526</v>
+        <v>-8.161</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.5835</v>
+        <v>-1.8166</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.2288</v>
+        <v>-3.9489</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.3411</v>
+        <v>-3.9053</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.5446</v>
+        <v>-5.4386</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.0077</v>
+        <v>-3.0106</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0501</v>
+        <v>0.0436</v>
       </c>
       <c r="M2" t="n">
-        <v>20.8325</v>
+        <v>0.4663</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8877</v>
+        <v>12.1986</v>
       </c>
     </row>
     <row r="3">
@@ -1680,41 +1840,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(-3.0, -1.04515]</t>
+          <t>(-3, -1]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>571</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2462</v>
+        <v>0.2792</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.3917</v>
+        <v>-4.2511</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6268</v>
+        <v>0.4174</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.8628</v>
+        <v>-1.8744</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8726</v>
+        <v>-1.8739</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.9923</v>
+        <v>-2.9984</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.0933</v>
+        <v>-1.0038</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3036</v>
+        <v>0.0005</v>
       </c>
       <c r="M3" t="n">
-        <v>20.189</v>
+        <v>0.3587</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0098</v>
+        <v>28.5933</v>
       </c>
     </row>
     <row r="4">
@@ -1728,41 +1888,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(-1.04515, 0.02845]</t>
+          <t>(-1, 0]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47</v>
+        <v>410</v>
       </c>
       <c r="E4" t="n">
-        <v>0.241</v>
+        <v>0.2005</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.597</v>
+        <v>-2.1524</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8143</v>
+        <v>0.9906</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4789</v>
+        <v>-0.4978</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4945</v>
+        <v>-0.4919</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.997</v>
+        <v>-0.9971</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0041</v>
+        <v>-0.0016</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3999</v>
+        <v>0.0059</v>
       </c>
       <c r="M4" t="n">
-        <v>868.1662</v>
+        <v>0.382</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0156</v>
+        <v>239.9911</v>
       </c>
     </row>
     <row r="5">
@@ -1776,41 +1936,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(0.02845, 0.995]</t>
+          <t>(0, 1]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>377</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2051</v>
+        <v>0.1844</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6851</v>
+        <v>-1.2935</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7448</v>
+        <v>2.1824</v>
       </c>
       <c r="H5" t="n">
-        <v>0.496</v>
+        <v>0.474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.506</v>
+        <v>0.4668</v>
       </c>
       <c r="J5" t="n">
-        <v>0.061</v>
+        <v>0.0024</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9731</v>
+        <v>0.9971</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4332</v>
+        <v>-0.0072</v>
       </c>
       <c r="M5" t="n">
-        <v>218.2896</v>
+        <v>0.402</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01</v>
+        <v>219.1195</v>
       </c>
     </row>
     <row r="6">
@@ -1824,137 +1984,139 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(0.995, 2.2125]</t>
+          <t>(1, 3]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>42</v>
+        <v>402</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2154</v>
+        <v>0.1966</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7953</v>
+        <v>0.0595</v>
       </c>
       <c r="G6" t="n">
-        <v>5.0809</v>
+        <v>3.7087</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2371</v>
+        <v>1.8239</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8323</v>
+        <v>1.8362</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0169</v>
+        <v>1.0044</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2125</v>
+        <v>2.9987</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6138</v>
+        <v>0.0123</v>
       </c>
       <c r="M6" t="n">
-        <v>24.7272</v>
+        <v>0.3635</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4048</v>
+        <v>36.9347</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>验证集</t>
+          <t>训练集</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[-3.2373, -3.05565]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0408</v>
+        <v>0.0406</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.8501</v>
+        <v>2.1431</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9912</v>
+        <v>7.4881</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9207</v>
+        <v>3.7439</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.2004</v>
+        <v>3.5758</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.2373</v>
+        <v>3.0026</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.1635</v>
+        <v>4.2053</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9664</v>
+        <v>-0.1681</v>
       </c>
       <c r="M7" t="n">
-        <v>40.2092</v>
+        <v>0.6242</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2797</v>
+        <v>16.7473</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>验证集</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
+          <t>训练集</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(-3.05565, -1.0134]</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>2045</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2653</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.0899</v>
+        <v>-8.161</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9526</v>
+        <v>7.4881</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9303</v>
+        <v>-0.4154</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0607</v>
+        <v>-0.4154</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.9478</v>
+        <v>-5.4386</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1178</v>
+        <v>4.2053</v>
       </c>
       <c r="L8" t="n">
-        <v>0.644</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>40.12</v>
+        <v>0.3937</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1304</v>
+        <v>105.6396</v>
       </c>
     </row>
     <row r="9">
@@ -1964,45 +2126,45 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(-1.0134, 0.0951]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1837</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5386</v>
+        <v>-7.2526</v>
       </c>
       <c r="G9" t="n">
-        <v>0.42</v>
+        <v>-2.7269</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.493</v>
+        <v>-4.1072</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5231</v>
+        <v>-3.976</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.909</v>
+        <v>-5.4514</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.105</v>
+        <v>-3.0337</v>
       </c>
       <c r="L9" t="n">
-        <v>0.545</v>
+        <v>0.1312</v>
       </c>
       <c r="M9" t="n">
-        <v>105.3176</v>
+        <v>0.5016</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0301</v>
+        <v>12.1286</v>
       </c>
     </row>
     <row r="10">
@@ -2012,45 +2174,45 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(0.0951, 0.9475]</t>
+          <t>(-3, -1]</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2041</v>
+        <v>0.3379</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2445</v>
+        <v>-4.0501</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1932</v>
+        <v>-0.1919</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5241</v>
+        <v>-1.9466</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6108</v>
+        <v>-1.9382</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2952</v>
+        <v>-2.9838</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8474</v>
+        <v>-1.0096</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3659</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>212.9946</v>
+        <v>0.4055</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0867</v>
+        <v>28.7133</v>
       </c>
     </row>
     <row r="11">
@@ -2060,237 +2222,239 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(0.9475, 2.1773]</t>
+          <t>(-1, 0]</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3061</v>
+        <v>0.1758</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0324</v>
+        <v>-1.7147</v>
       </c>
       <c r="G11" t="n">
-        <v>5.303</v>
+        <v>1.1056</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4545</v>
+        <v>-0.4602</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8955</v>
+        <v>-0.4655</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0476</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1773</v>
+        <v>-0.0005</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8884</v>
+        <v>-0.0053</v>
       </c>
       <c r="M11" t="n">
-        <v>32.8895</v>
+        <v>0.4303</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5590000000000001</v>
+        <v>181.8863</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OOT</t>
+          <t>验证集</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[-3.5586, -2.9993]</t>
+          <t>(0, 1]</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>227</v>
+        <v>96</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0824</v>
+        <v>0.1875</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.161</v>
+        <v>-1.0631</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8392</v>
+        <v>1.6018</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.008</v>
+        <v>0.3721</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.3274</v>
+        <v>0.4528</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.5586</v>
+        <v>0.0097</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.0004</v>
+        <v>0.9777</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8722</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>19.5421</v>
+        <v>0.3692</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6806</v>
+        <v>157.7609</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OOT</t>
+          <t>验证集</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(-2.9993, -1.0015]</t>
+          <t>(1, 3]</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>755</v>
+        <v>79</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2739</v>
+        <v>0.1543</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.3183</v>
+        <v>-0.4289</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0359</v>
+        <v>3.6213</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.0492</v>
+        <v>1.7949</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.9774</v>
+        <v>1.8028</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.9982</v>
+        <v>1.0031</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.0038</v>
+        <v>2.9457</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4569</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>33.9955</v>
+        <v>0.423</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0718</v>
+        <v>197.7507</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OOT</t>
+          <t>验证集</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(-1.0015, -0.00045]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>582</v>
+        <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2112</v>
+        <v>0.0527</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.7568</v>
+        <v>1.9567</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3536</v>
+        <v>6.3529</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6124000000000001</v>
+        <v>3.7315</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.512</v>
+        <v>3.599</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9992</v>
+        <v>3.0528</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0014</v>
+        <v>4.1762</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4461</v>
+        <v>-0.1325</v>
       </c>
       <c r="M14" t="n">
-        <v>152.783</v>
+        <v>0.5024</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1004</v>
+        <v>13.5929</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OOT</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
+          <t>验证集</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(-0.00045, 1.001]</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>589</v>
+        <v>512</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2137</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7397</v>
+        <v>-7.2526</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3518</v>
+        <v>6.3529</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4532</v>
+        <v>-0.5722</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5481</v>
+        <v>-0.5488</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0005</v>
+        <v>-5.4514</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9994</v>
+        <v>4.1762</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4603</v>
+        <v>0.0234</v>
       </c>
       <c r="M15" t="n">
-        <v>256.7787</v>
+        <v>0.4197</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0949</v>
+        <v>103.5968</v>
       </c>
     </row>
     <row r="16">
@@ -2300,48 +2464,348 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[-inf, -3]</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-6.5133</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-2.5382</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-3.8021</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-3.8118</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-5.2661</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-3.0204</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="N16" t="n">
+        <v>9.889200000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>(-3, -1]</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>123</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-3.668</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-1.8738</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1.852</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.9275</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1.0124</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="N17" t="n">
+        <v>64.78270000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>(-1, 0]</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>90</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2032</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-2.3095</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.2216</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.5021</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.471</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.9979</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.0094</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="N18" t="n">
+        <v>165.2947</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>(0, 1]</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>93</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2099</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.7397</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4751</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4592</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.4669</v>
+      </c>
+      <c r="N19" t="n">
+        <v>130.5052</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>5</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>(1.001, 2.211]</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>603</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.2188</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.1634</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>(1, 3]</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>79</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.1125</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.6625</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.7879</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.8395</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.0232</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.9629</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.4092</v>
+      </c>
+      <c r="N20" t="n">
+        <v>55.3971</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>(3, +inf]</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>23</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.9597</v>
+      </c>
+      <c r="G21" t="n">
         <v>7.636</v>
       </c>
-      <c r="H16" t="n">
-        <v>2.2296</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.819</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.0026</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.211</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.7359</v>
-      </c>
-      <c r="M16" t="n">
-        <v>46.7126</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.4106</v>
+      <c r="H21" t="n">
+        <v>4.1824</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.6759</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.0066</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1374</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.5065</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.6193</v>
+      </c>
+      <c r="N21" t="n">
+        <v>12.7008</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>443</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-6.5133</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7.636</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.2869</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.2958</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-5.2661</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.1374</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="N22" t="n">
+        <v>90.28530000000001</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="N2:N22">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2352,7 +2816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2363,7 +2827,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>[-3.03, -3]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2387,6 +2851,11 @@
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>(3, +inf]</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
@@ -2404,24 +2873,26 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[-3.03, -3]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.5</v>
+        <v>10.27</v>
       </c>
       <c r="C3" t="n">
-        <v>10.15</v>
+        <v>18.24</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>18.95</v>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>11.75</v>
       </c>
     </row>
     <row r="4">
@@ -2431,18 +2902,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.42</v>
+        <v>23.23</v>
       </c>
       <c r="C4" t="n">
-        <v>15.22</v>
+        <v>17.22</v>
       </c>
       <c r="D4" t="n">
-        <v>44.42</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>46.34</v>
+      </c>
+      <c r="E4" t="n">
+        <v>110.43</v>
+      </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>20.02</v>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>21.56</v>
       </c>
     </row>
     <row r="5">
@@ -2453,17 +2927,18 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>99.83</v>
+        <v>126.28</v>
       </c>
       <c r="D5" t="n">
-        <v>85.31999999999999</v>
+        <v>124.13</v>
       </c>
       <c r="E5" t="n">
-        <v>254.35</v>
+        <v>696.86</v>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>121.11</v>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>230.89</v>
       </c>
     </row>
     <row r="6">
@@ -2473,18 +2948,21 @@
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>364.24</v>
+      </c>
       <c r="D6" t="n">
-        <v>3459.94</v>
+        <v>781.65</v>
       </c>
       <c r="E6" t="n">
-        <v>284.79</v>
+        <v>124.38</v>
       </c>
       <c r="F6" t="n">
-        <v>32.13</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1170.67</v>
+        <v>148.74</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>268.52</v>
       </c>
     </row>
     <row r="7">
@@ -2497,19 +2975,22 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>43.15</v>
+        <v>47.8</v>
       </c>
       <c r="F7" t="n">
-        <v>18.38</v>
+        <v>17.77</v>
       </c>
       <c r="G7" t="n">
-        <v>24.73</v>
+        <v>27.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>23.04</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>(3, 3.03]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -2517,10 +2998,13 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>43.09</v>
+        <v>16.8</v>
       </c>
       <c r="G8" t="n">
-        <v>43.09</v>
+        <v>13.24</v>
+      </c>
+      <c r="H8" t="n">
+        <v>14.22</v>
       </c>
     </row>
     <row r="9">
@@ -2530,22 +3014,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.83</v>
+        <v>12.2</v>
       </c>
       <c r="C9" t="n">
-        <v>20.19</v>
+        <v>28.59</v>
       </c>
       <c r="D9" t="n">
-        <v>868.17</v>
+        <v>239.99</v>
       </c>
       <c r="E9" t="n">
-        <v>218.29</v>
+        <v>219.12</v>
       </c>
       <c r="F9" t="n">
-        <v>24.73</v>
+        <v>36.93</v>
       </c>
       <c r="G9" t="n">
-        <v>266.25</v>
+        <v>16.75</v>
+      </c>
+      <c r="H9" t="n">
+        <v>105.64</v>
       </c>
     </row>
     <row r="10">
@@ -2556,6 +3043,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2569,18 +3057,19 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[-3.03, -3]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>172</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -2592,7 +3081,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -2602,22 +3094,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>475</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>51</v>
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>581</v>
       </c>
     </row>
     <row r="14">
@@ -2630,19 +3125,22 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>255</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>382</v>
       </c>
     </row>
     <row r="15">
@@ -2655,19 +3153,22 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>240</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>38</v>
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>381</v>
       </c>
     </row>
     <row r="16">
@@ -2686,19 +3187,22 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="G16" t="n">
-        <v>39</v>
+        <v>20</v>
+      </c>
+      <c r="H16" t="n">
+        <v>403</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>(3, 3.03]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2714,10 +3218,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>63</v>
+      </c>
+      <c r="H17" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -2727,22 +3234,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>202</v>
       </c>
       <c r="C18" t="n">
-        <v>48</v>
+        <v>571</v>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>410</v>
       </c>
       <c r="E18" t="n">
-        <v>40</v>
+        <v>377</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>402</v>
       </c>
       <c r="G18" t="n">
-        <v>195</v>
+        <v>83</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2045</v>
       </c>
     </row>
     <row r="19">
@@ -2753,6 +3263,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2766,18 +3277,19 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[-3.03, -3]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0872</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0154</v>
+        <v>0.0191</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2789,7 +3301,10 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1026</v>
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1032</v>
       </c>
     </row>
     <row r="22">
@@ -2799,22 +3314,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0051</v>
+        <v>0.0147</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2154</v>
+        <v>0.2323</v>
       </c>
       <c r="D22" t="n">
-        <v>0.041</v>
+        <v>0.0362</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2615</v>
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.2841</v>
       </c>
     </row>
     <row r="23">
@@ -2827,19 +3345,22 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0154</v>
+        <v>0.0274</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1436</v>
+        <v>0.1247</v>
       </c>
       <c r="E23" t="n">
-        <v>0.041</v>
+        <v>0.0347</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1868</v>
       </c>
     </row>
     <row r="24">
@@ -2852,19 +3373,22 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0564</v>
+        <v>0.0396</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1128</v>
+        <v>0.1174</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0256</v>
+        <v>0.0289</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1949</v>
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1863</v>
       </c>
     </row>
     <row r="25">
@@ -2883,19 +3407,22 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0513</v>
+        <v>0.0313</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1487</v>
+        <v>0.156</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2</v>
+        <v>0.0098</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1971</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>(3, 3.03]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2911,10 +3438,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.041</v>
+        <v>0.0117</v>
       </c>
       <c r="G26" t="n">
-        <v>0.041</v>
+        <v>0.0308</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0425</v>
       </c>
     </row>
     <row r="27">
@@ -2924,21 +3454,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0988</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2462</v>
+        <v>0.2792</v>
       </c>
       <c r="D27" t="n">
-        <v>0.241</v>
+        <v>0.2005</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2051</v>
+        <v>0.1844</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2154</v>
+        <v>0.1966</v>
       </c>
       <c r="G27" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="H27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2950,6 +3483,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2963,24 +3497,26 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[-3.03, -3]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.83</v>
+        <v>11.71</v>
       </c>
       <c r="C30" t="n">
-        <v>27.92</v>
+        <v>18.57</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="n">
-        <v>22.88</v>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>13.62</v>
       </c>
     </row>
     <row r="31">
@@ -2990,18 +3526,21 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>62.58</v>
+        <v>18.27</v>
       </c>
       <c r="C31" t="n">
-        <v>32.69</v>
+        <v>19.06</v>
       </c>
       <c r="D31" t="n">
-        <v>52.87</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+        <v>46.77</v>
+      </c>
+      <c r="E31" t="n">
+        <v>103.48</v>
+      </c>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="n">
-        <v>38.72</v>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>22.56</v>
       </c>
     </row>
     <row r="32">
@@ -3012,17 +3551,20 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>133.99</v>
+        <v>107.38</v>
       </c>
       <c r="D32" t="n">
-        <v>18.87</v>
+        <v>155.96</v>
       </c>
       <c r="E32" t="n">
-        <v>220.77</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="n">
-        <v>82.27</v>
+        <v>317.68</v>
+      </c>
+      <c r="F32" t="n">
+        <v>358.34</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>184.73</v>
       </c>
     </row>
     <row r="33">
@@ -3034,14 +3576,17 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>244.22</v>
+        <v>367.34</v>
       </c>
       <c r="E33" t="n">
-        <v>234.67</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="n">
-        <v>237.27</v>
+        <v>127.1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1397.42</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>317.4</v>
       </c>
     </row>
     <row r="34">
@@ -3052,21 +3597,26 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>117.69</v>
+      </c>
       <c r="E34" t="n">
-        <v>31.81</v>
+        <v>40.87</v>
       </c>
       <c r="F34" t="n">
-        <v>27.25</v>
+        <v>19.01</v>
       </c>
       <c r="G34" t="n">
-        <v>27.66</v>
+        <v>41.14</v>
+      </c>
+      <c r="H34" t="n">
+        <v>24.49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>(3, 3.03]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -3074,10 +3624,13 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>44.17</v>
+        <v>18.53</v>
       </c>
       <c r="G35" t="n">
-        <v>44.17</v>
+        <v>10.15</v>
+      </c>
+      <c r="H35" t="n">
+        <v>11.83</v>
       </c>
     </row>
     <row r="36">
@@ -3087,22 +3640,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>40.21</v>
+        <v>12.13</v>
       </c>
       <c r="C36" t="n">
-        <v>40.12</v>
+        <v>28.71</v>
       </c>
       <c r="D36" t="n">
-        <v>105.32</v>
+        <v>181.89</v>
       </c>
       <c r="E36" t="n">
-        <v>212.99</v>
+        <v>157.76</v>
       </c>
       <c r="F36" t="n">
-        <v>32.89</v>
+        <v>197.75</v>
       </c>
       <c r="G36" t="n">
-        <v>85.17</v>
+        <v>13.59</v>
+      </c>
+      <c r="H36" t="n">
+        <v>103.6</v>
       </c>
     </row>
     <row r="37">
@@ -3113,6 +3669,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3126,18 +3683,19 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[-3.03, -3]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3149,7 +3707,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="40">
@@ -3159,22 +3720,25 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>137</v>
+      </c>
+      <c r="D40" t="n">
+        <v>17</v>
+      </c>
+      <c r="E40" t="n">
         <v>1</v>
       </c>
-      <c r="C40" t="n">
-        <v>11</v>
-      </c>
-      <c r="D40" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>158</v>
       </c>
     </row>
     <row r="41">
@@ -3187,19 +3751,22 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
+        <v>19</v>
+      </c>
+      <c r="D41" t="n">
+        <v>52</v>
+      </c>
+      <c r="E41" t="n">
+        <v>21</v>
+      </c>
+      <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="D41" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
       <c r="G41" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="42">
@@ -3215,16 +3782,19 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E42" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G42" t="n">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="43">
@@ -3240,22 +3810,25 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="G43" t="n">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>(3, 3.03]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -3271,10 +3844,13 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>5</v>
+        <v>24</v>
+      </c>
+      <c r="H44" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="45">
@@ -3284,22 +3860,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="C45" t="n">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="E45" t="n">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="G45" t="n">
-        <v>49</v>
+        <v>27</v>
+      </c>
+      <c r="H45" t="n">
+        <v>512</v>
       </c>
     </row>
     <row r="46">
@@ -3310,6 +3889,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3323,18 +3903,19 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[-3.03, -3]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0204</v>
+        <v>0.0859</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0204</v>
+        <v>0.0332</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -3346,7 +3927,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0408</v>
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.1191</v>
       </c>
     </row>
     <row r="49">
@@ -3356,22 +3940,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0204</v>
+        <v>0.0059</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2245</v>
+        <v>0.2676</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0612</v>
+        <v>0.0332</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3061</v>
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.3086</v>
       </c>
     </row>
     <row r="50">
@@ -3384,19 +3971,22 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0204</v>
+        <v>0.0371</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0612</v>
+        <v>0.1016</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0204</v>
+        <v>0.041</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="G50" t="n">
-        <v>0.102</v>
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.1816</v>
       </c>
     </row>
     <row r="51">
@@ -3412,16 +4002,19 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0612</v>
+        <v>0.0391</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1633</v>
+        <v>0.1211</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>0.0195</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2245</v>
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.1797</v>
       </c>
     </row>
     <row r="52">
@@ -3437,22 +4030,25 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0204</v>
+        <v>0.0234</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2041</v>
+        <v>0.1211</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2245</v>
+        <v>0.0059</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1523</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>(3, 3.03]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -3468,10 +4064,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.102</v>
+        <v>0.0117</v>
       </c>
       <c r="G53" t="n">
-        <v>0.102</v>
+        <v>0.0469</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.0586</v>
       </c>
     </row>
     <row r="54">
@@ -3481,21 +4080,24 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.0408</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2653</v>
+        <v>0.3379</v>
       </c>
       <c r="D54" t="n">
-        <v>0.1837</v>
+        <v>0.1758</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2041</v>
+        <v>0.1875</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3061</v>
+        <v>0.1543</v>
       </c>
       <c r="G54" t="n">
+        <v>0.0527</v>
+      </c>
+      <c r="H54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3507,6 +4109,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3520,24 +4123,26 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>[-3.03, -3]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>18.91</v>
+        <v>7.59</v>
       </c>
       <c r="C57" t="n">
-        <v>23.14</v>
+        <v>24.2</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="n">
-        <v>20.24</v>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="n">
+        <v>11.63</v>
       </c>
     </row>
     <row r="58">
@@ -3547,20 +4152,21 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>23.7</v>
+        <v>19.09</v>
       </c>
       <c r="C58" t="n">
-        <v>20.85</v>
+        <v>17.69</v>
       </c>
       <c r="D58" t="n">
-        <v>48.9</v>
+        <v>42.59</v>
       </c>
       <c r="E58" t="n">
-        <v>127.33</v>
+        <v>104.24</v>
       </c>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="n">
-        <v>27.56</v>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>22.86</v>
       </c>
     </row>
     <row r="59">
@@ -3571,19 +4177,20 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>126.05</v>
+        <v>168.97</v>
       </c>
       <c r="D59" t="n">
-        <v>118.88</v>
+        <v>106.3</v>
       </c>
       <c r="E59" t="n">
-        <v>614.2</v>
+        <v>332.75</v>
       </c>
       <c r="F59" t="n">
-        <v>1188.42</v>
-      </c>
-      <c r="G59" t="n">
-        <v>249.36</v>
+        <v>1087.91</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>177.94</v>
       </c>
     </row>
     <row r="60">
@@ -3594,19 +4201,20 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>3428.28</v>
+        <v>3633.62</v>
       </c>
       <c r="D60" t="n">
-        <v>433.05</v>
+        <v>468.84</v>
       </c>
       <c r="E60" t="n">
-        <v>193.41</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>165.86</v>
-      </c>
-      <c r="G60" t="n">
-        <v>242.64</v>
+        <v>191.12</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="n">
+        <v>235.19</v>
       </c>
     </row>
     <row r="61">
@@ -3618,35 +4226,39 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>118.91</v>
+        <v>100.77</v>
       </c>
       <c r="E61" t="n">
-        <v>45.51</v>
+        <v>52.22</v>
       </c>
       <c r="F61" t="n">
-        <v>20.87</v>
+        <v>17.64</v>
       </c>
       <c r="G61" t="n">
-        <v>26.75</v>
+        <v>13.71</v>
+      </c>
+      <c r="H61" t="n">
+        <v>27.53</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>(3, 3.03]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="n">
-        <v>77.29000000000001</v>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>43.78</v>
+        <v>18.54</v>
       </c>
       <c r="G62" t="n">
-        <v>44.04</v>
+        <v>12.6</v>
+      </c>
+      <c r="H62" t="n">
+        <v>13.75</v>
       </c>
     </row>
     <row r="63">
@@ -3656,22 +4268,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>19.54</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>34</v>
+        <v>64.78</v>
       </c>
       <c r="D63" t="n">
-        <v>152.78</v>
+        <v>165.29</v>
       </c>
       <c r="E63" t="n">
-        <v>256.78</v>
+        <v>130.51</v>
       </c>
       <c r="F63" t="n">
-        <v>46.71</v>
+        <v>55.4</v>
       </c>
       <c r="G63" t="n">
-        <v>108.28</v>
+        <v>12.7</v>
+      </c>
+      <c r="H63" t="n">
+        <v>90.29000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -3682,6 +4297,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3695,18 +4311,19 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>[-3.03, -3]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>197</v>
+        <v>28</v>
       </c>
       <c r="C66" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3718,7 +4335,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>287</v>
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="67">
@@ -3728,22 +4348,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C67" t="n">
-        <v>604</v>
+        <v>99</v>
       </c>
       <c r="D67" t="n">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="E67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>800</v>
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>127</v>
       </c>
     </row>
     <row r="68">
@@ -3756,19 +4379,22 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="D68" t="n">
-        <v>324</v>
+        <v>52</v>
       </c>
       <c r="E68" t="n">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>517</v>
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="69">
@@ -3784,16 +4410,19 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="E69" t="n">
-        <v>333</v>
+        <v>49</v>
       </c>
       <c r="F69" t="n">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="G69" t="n">
-        <v>503</v>
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="70">
@@ -3809,22 +4438,25 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>23</v>
+      </c>
+      <c r="F70" t="n">
+        <v>62</v>
+      </c>
+      <c r="G70" t="n">
         <v>2</v>
       </c>
-      <c r="E70" t="n">
-        <v>116</v>
-      </c>
-      <c r="F70" t="n">
-        <v>401</v>
-      </c>
-      <c r="G70" t="n">
-        <v>519</v>
+      <c r="H70" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>(3, 3.03]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3837,13 +4469,16 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>130</v>
+        <v>21</v>
+      </c>
+      <c r="H71" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="72">
@@ -3853,22 +4488,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>227</v>
+        <v>35</v>
       </c>
       <c r="C72" t="n">
-        <v>755</v>
+        <v>123</v>
       </c>
       <c r="D72" t="n">
-        <v>582</v>
+        <v>90</v>
       </c>
       <c r="E72" t="n">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="F72" t="n">
-        <v>603</v>
+        <v>79</v>
       </c>
       <c r="G72" t="n">
-        <v>2756</v>
+        <v>23</v>
+      </c>
+      <c r="H72" t="n">
+        <v>443</v>
       </c>
     </row>
     <row r="73">
@@ -3879,6 +4517,7 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3892,18 +4531,19 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>[-3.03, -3]</t>
+          <t>[-inf, -3]</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0327</v>
+        <v>0.0203</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3915,7 +4555,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1041</v>
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.0835</v>
       </c>
     </row>
     <row r="76">
@@ -3925,22 +4568,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.0109</v>
+        <v>0.0158</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2192</v>
+        <v>0.2235</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0573</v>
+        <v>0.0429</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0029</v>
+        <v>0.0045</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2903</v>
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.2867</v>
       </c>
     </row>
     <row r="77">
@@ -3953,19 +4599,22 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0218</v>
+        <v>0.0316</v>
       </c>
       <c r="D77" t="n">
-        <v>0.1176</v>
+        <v>0.1174</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0475</v>
+        <v>0.0429</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0007</v>
+        <v>0.0023</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1876</v>
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.1941</v>
       </c>
     </row>
     <row r="78">
@@ -3978,19 +4627,22 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0004</v>
+        <v>0.0023</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0356</v>
+        <v>0.0406</v>
       </c>
       <c r="E78" t="n">
-        <v>0.1208</v>
+        <v>0.1106</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0258</v>
+        <v>0.0248</v>
       </c>
       <c r="G78" t="n">
-        <v>0.1825</v>
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.1783</v>
       </c>
     </row>
     <row r="79">
@@ -4006,22 +4658,25 @@
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0007</v>
+        <v>0.0023</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0421</v>
+        <v>0.0519</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1455</v>
+        <v>0.14</v>
       </c>
       <c r="G79" t="n">
-        <v>0.1883</v>
+        <v>0.0045</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.1986</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>(3, 3.03]</t>
+          <t>(3, +inf]</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -4034,13 +4689,16 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0468</v>
+        <v>0.0113</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0472</v>
+        <v>0.0474</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0587</v>
       </c>
     </row>
     <row r="81">
@@ -4050,25 +4708,116 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0824</v>
+        <v>0.079</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2739</v>
+        <v>0.2777</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2112</v>
+        <v>0.2032</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2137</v>
+        <v>0.2099</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2188</v>
+        <v>0.1783</v>
       </c>
       <c r="G81" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="H81" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="82"/>
   </sheetData>
+  <conditionalFormatting sqref="B3:G8">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00FF0000"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:G17">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:G26">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30:G35">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00FF0000"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:G44">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48:G53">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57:G62">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00FF0000"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B66:G71">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75:G80">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>